--- a/data/trans_dic/IP19C09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por otros motivos</t>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -614,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,99</t>
+          <t>0,0; 21,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,86</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,45</t>
+          <t>0,0; 12,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,0</t>
+          <t>0,0; 14,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,26</t>
+          <t>1,25; 10,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,22</t>
+          <t>0,0; 6,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 7,87</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -787,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,0; 5,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 10,84</t>
+          <t>1,28; 10,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,55</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,38</t>
+          <t>0,0; 7,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,69</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 5,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,72</t>
+          <t>0,61; 5,77</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,19</t>
+          <t>0,0; 13,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,31</t>
+          <t>0,0; 9,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,53</t>
+          <t>1,72; 13,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,71</t>
+          <t>0,0; 12,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,03</t>
+          <t>0,0; 11,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 7,41</t>
+          <t>0,86; 7,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 9,49</t>
+          <t>0,98; 10,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,71</t>
+          <t>0,0; 8,24</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,34</t>
+          <t>0,0; 8,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 14,98</t>
+          <t>1,28; 15,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,71</t>
+          <t>0,0; 8,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,32</t>
+          <t>1,42; 14,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,07</t>
+          <t>2,09; 11,01</t>
         </is>
       </c>
     </row>
@@ -1117,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 18,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,43</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,81</t>
+          <t>0,0; 17,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,31</t>
+          <t>0,0; 9,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,54</t>
+          <t>0,0; 12,22</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1227,54 +1228,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,33</t>
+          <t>0,0; 14,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,77</t>
+          <t>0,0; 8,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>0,0; 6,79</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,32</t>
+          <t>0,0; 11,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,01</t>
+          <t>0,0; 12,45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 6,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,16</t>
+          <t>0,82; 7,5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 5,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,61</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,43</t>
+          <t>0,48; 4,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1447,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,5</t>
+          <t>0,0; 5,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,97</t>
+          <t>0,73; 6,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 13,17</t>
+          <t>2,77; 12,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,49</t>
+          <t>0,95; 9,34</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,98</t>
+          <t>0,82; 8,25</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,62</t>
+          <t>1,96; 7,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,26</t>
+          <t>1,23; 5,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,29</t>
+          <t>1,26; 5,55</t>
         </is>
       </c>
     </row>
@@ -1557,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,67</t>
+          <t>0,64; 2,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,94</t>
+          <t>0,73; 3,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,1</t>
+          <t>1,37; 4,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,98</t>
+          <t>1,83; 4,72</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,52</t>
+          <t>0,84; 3,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,11</t>
+          <t>1,34; 4,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,32</t>
+          <t>1,44; 3,21</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,74</t>
+          <t>1,0; 2,71</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,55</t>
+          <t>1,66; 3,63</t>
         </is>
       </c>
     </row>
@@ -1626,4 +1627,1611 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1250</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1889</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4071</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3432</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3568</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4123</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>571; 4594</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3423</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4169</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1281</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1604</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2279</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3166</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5200</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>663; 5551</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3261</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4518</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4487</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5518</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>655; 6181</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1474</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2540</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4569</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3114</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>607; 4887</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5054</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3653</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>601; 4922</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>712; 7328</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5150</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2541</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5028</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3599</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>558; 6563</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3353</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>693; 6938</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4615</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3060</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1937; 10192</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4912</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3755</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4337</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4651</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4866</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3821</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1391</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2227</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3668</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3045</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2646</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3334</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4861</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4529</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4243</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>636; 5850</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>733</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3655</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3353</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4568</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>644; 5492</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3697</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2551</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5815</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3125</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4110</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>561; 5008</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>2063; 9201</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>667; 6549</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>627; 6286</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>3045; 10967</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>1802; 8034</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>1925; 8499</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15982</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>12224</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>17458</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>2232; 10004</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>2516; 11014</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>4764; 14960</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>6609; 17076</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3037; 12290</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4781; 15423</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10249; 22854</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>7098; 19184</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>11667; 25541</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Provincia-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,07</t>
+          <t>0,0; 19,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,94</t>
+          <t>0,0; 11,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,03</t>
+          <t>0,0; 14,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,38</t>
+          <t>0,0; 13,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,02</t>
+          <t>1,26; 11,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,67</t>
+          <t>0,0; 9,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,87</t>
+          <t>0,0; 8,06</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,53</t>
+          <t>0,0; 5,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 10,72</t>
+          <t>1,27; 11,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,92</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,77</t>
+          <t>0,61; 5,68</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,65</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,78</t>
+          <t>0,0; 12,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 13,83</t>
+          <t>1,72; 13,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,81</t>
+          <t>0,0; 13,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,91</t>
+          <t>0,0; 12,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,07</t>
+          <t>0,86; 7,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 10,05</t>
+          <t>0,99; 10,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,24</t>
+          <t>0,0; 8,21</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1013,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,75</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 15,04</t>
+          <t>1,82; 15,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,05</t>
+          <t>0,0; 8,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,22 +1033,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,42; 14,18</t>
+          <t>1,4; 14,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 11,01</t>
+          <t>1,96; 11,46</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,76</t>
+          <t>0,0; 17,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 22,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,12</t>
+          <t>0,0; 18,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,56</t>
+          <t>0,0; 9,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 9,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 13,54</t>
         </is>
       </c>
     </row>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,47</t>
+          <t>0,0; 11,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,6</t>
+          <t>0,0; 8,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,79</t>
+          <t>0,0; 8,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,76</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1253,22 +1253,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,45</t>
+          <t>0,0; 12,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,43</t>
+          <t>0,0; 8,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,36</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,5</t>
+          <t>0,83; 7,95</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,6</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 5,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,12</t>
+          <t>0,48; 4,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1453,42 +1453,42 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,42</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,52</t>
+          <t>0,73; 6,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 12,37</t>
+          <t>3,44; 12,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,34</t>
+          <t>0,96; 8,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,25</t>
+          <t>0,82; 8,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,04</t>
+          <t>1,7; 6,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,5</t>
+          <t>0,96; 5,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,55</t>
+          <t>1,21; 5,88</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,85</t>
+          <t>0,55; 2,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,18</t>
+          <t>0,77; 3,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,31</t>
+          <t>1,41; 4,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,72</t>
+          <t>1,93; 4,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,41</t>
+          <t>0,87; 3,34</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,33</t>
+          <t>1,32; 4,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,21</t>
+          <t>1,47; 3,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,71</t>
+          <t>1,0; 2,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,63</t>
+          <t>1,62; 3,58</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4071</t>
+          <t>0; 3774</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1876,32 +1876,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3432</t>
+          <t>0; 2947</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3568</t>
+          <t>0; 4318</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4123</t>
+          <t>0; 3847</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>571; 4594</t>
+          <t>579; 5072</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 4661</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4169</t>
+          <t>0; 4268</t>
         </is>
       </c>
     </row>
@@ -2024,27 +2024,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3166</t>
+          <t>0; 3126</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5200</t>
+          <t>0; 4595</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>663; 5551</t>
+          <t>657; 5952</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3261</t>
+          <t>0; 3600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 3684</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4487</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5518</t>
+          <t>0; 5510</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>655; 6181</t>
+          <t>654; 6087</t>
         </is>
       </c>
     </row>
@@ -2192,42 +2192,42 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4569</t>
+          <t>0; 4604</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3114</t>
+          <t>0; 3924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>607; 4887</t>
+          <t>606; 4891</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5054</t>
+          <t>0; 5185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3653</t>
+          <t>0; 3879</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>601; 4922</t>
+          <t>600; 5526</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>712; 7328</t>
+          <t>719; 7582</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5150</t>
+          <t>0; 5130</t>
         </is>
       </c>
     </row>
@@ -2355,17 +2355,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3599</t>
+          <t>0; 3448</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>558; 6563</t>
+          <t>792; 6619</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>0; 3369</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2375,22 +2375,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>693; 6938</t>
+          <t>686; 7300</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4615</t>
+          <t>0; 4287</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3060</t>
+          <t>0; 3683</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1937; 10192</t>
+          <t>1817; 10608</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4912</t>
+          <t>0; 4683</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3755</t>
+          <t>0; 3359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4337</t>
+          <t>0; 4750</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2543,17 +2543,17 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4651</t>
+          <t>0; 4568</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4866</t>
+          <t>0; 4857</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 3821</t>
+          <t>0; 4233</t>
         </is>
       </c>
     </row>
@@ -2676,22 +2676,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3668</t>
+          <t>0; 2970</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3045</t>
+          <t>0; 3062</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 3234</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3334</t>
+          <t>0; 3295</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4861</t>
+          <t>0; 4841</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4529</t>
+          <t>0; 4322</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 4243</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>636; 5850</t>
+          <t>645; 6202</t>
         </is>
       </c>
     </row>
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 4175</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3353</t>
+          <t>0; 3832</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 4073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2869,12 +2869,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>644; 5492</t>
+          <t>644; 5659</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3697</t>
+          <t>0; 3345</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3125</t>
+          <t>0; 3123</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4110</t>
+          <t>0; 4220</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>561; 5008</t>
+          <t>563; 5163</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2063; 9201</t>
+          <t>2557; 9427</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>667; 6549</t>
+          <t>670; 5919</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>627; 6286</t>
+          <t>624; 6204</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3045; 10967</t>
+          <t>2649; 10277</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1802; 8034</t>
+          <t>1402; 7869</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1925; 8499</t>
+          <t>1844; 8997</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2232; 10004</t>
+          <t>1936; 9331</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2516; 11014</t>
+          <t>2675; 11731</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4764; 14960</t>
+          <t>4889; 14753</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6609; 17076</t>
+          <t>6994; 17441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3037; 12290</t>
+          <t>3127; 12029</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4781; 15423</t>
+          <t>4692; 15426</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10249; 22854</t>
+          <t>10510; 23692</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>7098; 19184</t>
+          <t>7083; 19105</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11667; 25541</t>
+          <t>11418; 25186</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C09-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Provincia-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>6,47%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,54</t>
+          <t>0,0; 10,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 13,45</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 13,0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 22,99</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,11</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,56</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,42</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 11,06</t>
+          <t>1,25; 11,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,08</t>
+          <t>0,0; 8,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,06</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,46</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 9,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,26; 10,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,41</t>
+          <t>0,0; 3,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,68</t>
+          <t>0,62; 5,72</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,39%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1,72; 12,53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 10,71</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 14,03</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,76</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,33</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,72; 13,84</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,15</t>
+          <t>0,0; 15,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,65</t>
+          <t>0,0; 12,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,94</t>
+          <t>0,87; 7,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,4</t>
+          <t>0,97; 9,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,7%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 9,71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,38</t>
-        </is>
-      </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,17</t>
+          <t>1,4; 14,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,09</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 14,92</t>
+          <t>1,27; 14,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,51</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 11,46</t>
+          <t>2,08; 11,07</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,55%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>5,13%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 17,81</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 22,33</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0,0; 14,23</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 18,74</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 21,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,39</t>
+          <t>0,0; 11,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,73</t>
+          <t>0,0; 8,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,54</t>
+          <t>0,0; 14,54</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2,89%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2,11%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,64%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 12,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,29</t>
+          <t>0,0; 13,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 14,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,4</t>
+          <t>0,0; 8,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,05</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,95</t>
+          <t>0,81; 7,16</t>
         </is>
       </c>
     </row>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,4</t>
+          <t>0,0; 6,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,27 +1353,27 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,25</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,25</t>
+          <t>0,48; 4,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1395,32 +1395,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,8%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,48%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>3,35; 13,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,56</t>
+          <t>0,98; 9,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,72</t>
+          <t>0,82; 7,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 12,67</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,45</t>
+          <t>0,0; 5,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 8,14</t>
+          <t>0,74; 6,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,6</t>
+          <t>1,72; 6,62</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,39</t>
+          <t>1,22; 5,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,88</t>
+          <t>1,24; 5,29</t>
         </is>
       </c>
     </row>
@@ -1505,32 +1505,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,66</t>
+          <t>1,97; 4,98</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,39</t>
+          <t>0,82; 3,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,25</t>
+          <t>1,22; 4,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,82</t>
+          <t>0,58; 2,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,34</t>
+          <t>0,72; 2,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,33</t>
+          <t>1,2; 4,1</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,32</t>
+          <t>1,5; 3,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,7</t>
+          <t>1,05; 2,74</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,58</t>
+          <t>1,62; 3,55</t>
         </is>
       </c>
     </row>
@@ -1660,14 +1660,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1755,32 +1755,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1808,32 +1808,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>1250</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3774</t>
+          <t>0; 2880</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 3988</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3728</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4441</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2947</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4318</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3847</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>579; 5072</t>
+          <t>574; 5162</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4661</t>
+          <t>0; 4217</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4268</t>
+          <t>0; 4328</t>
         </is>
       </c>
     </row>
@@ -1928,22 +1928,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1971,32 +1971,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>632</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>950</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2279</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>654</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3126</t>
+          <t>0; 2955</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4595</t>
+          <t>0; 3640</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>657; 5952</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3600</t>
+          <t>0; 3184</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>0; 4679</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>655; 5614</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4172</t>
+          <t>0; 4509</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5510</t>
+          <t>0; 5527</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>654; 6087</t>
+          <t>667; 6128</t>
         </is>
       </c>
     </row>
@@ -2081,27 +2081,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -2134,32 +2134,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1833</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1474</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>759</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>606; 4427</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4223</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4304</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4604</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3924</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>606; 4891</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5185</t>
+          <t>0; 5082</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3879</t>
+          <t>0; 3917</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>600; 5526</t>
+          <t>603; 5158</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>719; 7582</t>
+          <t>710; 6920</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5130</t>
+          <t>0; 4821</t>
         </is>
       </c>
     </row>
@@ -2244,27 +2244,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2297,32 +2297,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2541</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>621</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2487</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>820</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2541</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 4043</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3448</t>
-        </is>
-      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>792; 6619</t>
+          <t>686; 7007</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3369</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3019</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>686; 7300</t>
+          <t>555; 6533</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4287</t>
+          <t>0; 4061</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3683</t>
+          <t>0; 2801</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1817; 10608</t>
+          <t>1925; 10244</t>
         </is>
       </c>
     </row>
@@ -2407,32 +2407,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2460,32 +2460,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>929</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>771</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4683</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>0; 4512</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>0; 3359</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0; 3728</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0; 4750</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3224</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4568</t>
+          <t>0; 5503</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 4857</t>
+          <t>0; 4226</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4233</t>
+          <t>0; 4547</t>
         </is>
       </c>
     </row>
@@ -2575,27 +2575,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>732</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>640</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1587</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2970</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3062</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3234</t>
+          <t>0; 5078</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3295</t>
+          <t>0; 3632</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4523</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4841</t>
+          <t>0; 3225</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 4082</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3473</t>
+          <t>0; 3063</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>645; 6202</t>
+          <t>634; 5585</t>
         </is>
       </c>
     </row>
@@ -2733,27 +2733,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2786,27 +2786,27 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1293</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>733</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>665</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1293</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4175</t>
+          <t>0; 4495</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 3832</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2854,27 +2854,27 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4073</t>
+          <t>0; 4408</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>0; 3359</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>644; 5659</t>
+          <t>641; 5901</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 3345</t>
+          <t>0; 3354</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2896,32 +2896,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -2949,32 +2949,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2551</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>616</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1191</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>1905</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5198</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2551</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 3123</t>
+          <t>2496; 9804</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 4220</t>
+          <t>685; 6650</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>563; 5163</t>
+          <t>627; 6076</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2557; 9427</t>
+          <t>0; 3444</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>670; 5919</t>
+          <t>0; 4174</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>624; 6204</t>
+          <t>571; 5356</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2649; 10277</t>
+          <t>2676; 10316</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>1402; 7869</t>
+          <t>1783; 7673</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1844; 8997</t>
+          <t>1903; 8097</t>
         </is>
       </c>
     </row>
@@ -3059,27 +3059,27 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3112,32 +3112,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>4893</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>8842</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1936; 9331</t>
+          <t>7123; 18017</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2675; 11731</t>
+          <t>2946; 12686</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4889; 14753</t>
+          <t>4364; 14639</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6994; 17441</t>
+          <t>2049; 9353</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>3127; 12029</t>
+          <t>2479; 10202</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4692; 15426</t>
+          <t>4151; 14237</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10510; 23692</t>
+          <t>10666; 23660</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>7083; 19105</t>
+          <t>7409; 19371</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>11418; 25186</t>
+          <t>11379; 24982</t>
         </is>
       </c>
     </row>
